--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Integracion.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Integracion.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Principios de integración" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.1 Integraciones internas — su" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 Integraciones externas — pl" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Contratos (RT-05.16 · RT-05." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.1 Eventos canónicos del domin" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Mensajería (RT-02.06 · RT-02" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Costuras híbridas — amarre c" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Versionado y política de obs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Gobierno de la capa de integ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Carga y descarga masiva de " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Referencias cruzadas con la" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Trazabilidad normativa (res" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1. Principios de integración" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="3.1 Integraciones internas — su" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3.2 Integraciones externas — pl" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Contratos (RT-05.16 · RT-05." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4.1 Eventos canónicos del domin" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Mensajería (RT-02.06 · RT-02" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Costuras híbridas — amarre c" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Versionado y política de obs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. Gobierno de la capa de integ" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. Carga y descarga masiva de " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="12. Referencias cruzadas con la" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="13. Trazabilidad normativa (res" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Orden garantizado por partición (MessageGroupId = sitio) y deduplicación; alimenta a celery-reconciliation y celery-erp-sync.</t>
+          <t>Sobres JSON versionados; orden garantizado por grupo (sitio y agregado de negocio) y deduplicación por el identificador del evento; los lee el consumidor PHP de reconciliación, que confirma solo tras persistir.</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>VM-04 ↔ celery-erp-sync</t>
+          <t>VM-04 ↔ erp-sync (trabajador Laravel), con clave idempotente por operación</t>
         </is>
       </c>
     </row>
